--- a/data/trans_orig/P24B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P24B-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2007</t>
+          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22965</t>
+          <t>23979</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13369</t>
+          <t>13229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29657</t>
+          <t>30627</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24659</t>
+          <t>24547</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46595</t>
+          <t>47313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>125383</t>
+          <t>125957</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>152770</t>
+          <t>152860</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84274</t>
+          <t>84572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109677</t>
+          <t>108028</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>218818</t>
+          <t>219848</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256611</t>
+          <t>256073</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,3%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39356</t>
+          <t>40241</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65236</t>
+          <t>63333</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40953</t>
+          <t>41341</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63691</t>
+          <t>64061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>85850</t>
+          <t>86820</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>120689</t>
+          <t>120180</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40717</t>
+          <t>40719</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69249</t>
+          <t>68608</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39130</t>
+          <t>40090</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65134</t>
+          <t>65697</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87650</t>
+          <t>87706</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126622</t>
+          <t>124438</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>272908</t>
+          <t>273096</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>308558</t>
+          <t>307534</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>118316</t>
+          <t>118043</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>149766</t>
+          <t>147828</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>399218</t>
+          <t>401729</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>447295</t>
+          <t>447856</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42363</t>
+          <t>43039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69987</t>
+          <t>71862</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36810</t>
+          <t>36533</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60865</t>
+          <t>61673</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85703</t>
+          <t>85059</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122746</t>
+          <t>122666</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41700</t>
+          <t>40931</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68841</t>
+          <t>70412</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33954</t>
+          <t>34728</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59751</t>
+          <t>59948</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83429</t>
+          <t>82640</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>121168</t>
+          <t>121444</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>223737</t>
+          <t>223258</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>257556</t>
+          <t>258871</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151923</t>
+          <t>150578</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182537</t>
+          <t>181928</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>384172</t>
+          <t>378530</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>429627</t>
+          <t>430951</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,11%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33896</t>
+          <t>32554</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59878</t>
+          <t>58555</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33053</t>
+          <t>33314</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57880</t>
+          <t>59455</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>74895</t>
+          <t>73007</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>109535</t>
+          <t>108159</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21899</t>
+          <t>21710</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43166</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>21089</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39785</t>
+          <t>41583</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46647</t>
+          <t>46550</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77436</t>
+          <t>75258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159867</t>
+          <t>160041</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188524</t>
+          <t>188220</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80213</t>
+          <t>80736</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103930</t>
+          <t>104152</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>248563</t>
+          <t>250865</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>286155</t>
+          <t>284576</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,15%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18374</t>
+          <t>17707</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40002</t>
+          <t>38662</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15081</t>
+          <t>14842</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33684</t>
+          <t>31188</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37574</t>
+          <t>37670</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65024</t>
+          <t>64592</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20888</t>
+          <t>21064</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40136</t>
+          <t>40193</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15897</t>
+          <t>15085</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29144</t>
+          <t>29213</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51035</t>
+          <t>50675</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77904</t>
+          <t>79449</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100130</t>
+          <t>99725</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24111</t>
+          <t>23865</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37045</t>
+          <t>37069</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>106763</t>
+          <t>107150</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>131472</t>
+          <t>130460</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,3%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15731</t>
+          <t>15761</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14608</t>
+          <t>14727</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>10233</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25886</t>
+          <t>24899</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11381</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23802</t>
+          <t>24850</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>855</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14052</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27884</t>
+          <t>27626</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24626</t>
+          <t>24075</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37982</t>
+          <t>38213</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26579</t>
+          <t>26899</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40829</t>
+          <t>41260</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>69,05%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9007</t>
+          <t>9089</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18187</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>9644</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20082</t>
+          <t>19925</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,02%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>12959</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>16325</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,83%</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>190066</t>
+          <t>189440</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>243889</t>
+          <t>242929</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>137901</t>
+          <t>138394</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>185240</t>
+          <t>184899</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>340357</t>
+          <t>340076</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>413113</t>
+          <t>412919</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>940124</t>
+          <t>939685</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1007518</t>
+          <t>1008922</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>500371</t>
+          <t>499663</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>557430</t>
+          <t>555900</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1456691</t>
+          <t>1455238</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1544929</t>
+          <t>1549496</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,97%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>167205</t>
+          <t>164819</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>217492</t>
+          <t>218636</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>152551</t>
+          <t>155027</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>200007</t>
+          <t>200549</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>335468</t>
+          <t>335610</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>404987</t>
+          <t>405865</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2012</t>
+          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35114</t>
+          <t>33597</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58530</t>
+          <t>57836</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25258</t>
+          <t>24973</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46025</t>
+          <t>47343</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65865</t>
+          <t>66746</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97451</t>
+          <t>97246</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67087</t>
+          <t>69514</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93973</t>
+          <t>95343</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57843</t>
+          <t>56915</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82945</t>
+          <t>82106</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133913</t>
+          <t>133859</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>169035</t>
+          <t>169479</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,09%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28724</t>
+          <t>27923</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49696</t>
+          <t>48703</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32152</t>
+          <t>34422</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54963</t>
+          <t>56165</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67411</t>
+          <t>67132</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>98390</t>
+          <t>97718</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84044</t>
+          <t>84389</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>118489</t>
+          <t>118870</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61155</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89110</t>
+          <t>89498</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154024</t>
+          <t>153349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>201890</t>
+          <t>199306</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>169457</t>
+          <t>169577</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>208408</t>
+          <t>206227</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>104704</t>
+          <t>106081</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>136969</t>
+          <t>137062</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>285125</t>
+          <t>286570</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>335053</t>
+          <t>336012</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,22%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46018</t>
+          <t>47498</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75622</t>
+          <t>76737</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39184</t>
+          <t>39980</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65212</t>
+          <t>65323</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92445</t>
+          <t>92702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131893</t>
+          <t>132102</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66738</t>
+          <t>67546</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99689</t>
+          <t>99657</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46504</t>
+          <t>45928</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73467</t>
+          <t>74792</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>121476</t>
+          <t>122301</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>163957</t>
+          <t>165222</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>164572</t>
+          <t>166310</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>201971</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115912</t>
+          <t>115138</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147107</t>
+          <t>147593</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>291821</t>
+          <t>290711</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>339712</t>
+          <t>340612</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,48%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44515</t>
+          <t>44373</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72841</t>
+          <t>74884</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42863</t>
+          <t>43985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70748</t>
+          <t>72048</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>95979</t>
+          <t>96235</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>137024</t>
+          <t>134968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65390</t>
+          <t>65270</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96730</t>
+          <t>97496</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46995</t>
+          <t>46170</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73532</t>
+          <t>75509</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120462</t>
+          <t>120756</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>162540</t>
+          <t>163981</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>146337</t>
+          <t>145110</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>181193</t>
+          <t>180682</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119990</t>
+          <t>118160</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>151617</t>
+          <t>151781</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>275915</t>
+          <t>273745</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>323578</t>
+          <t>321761</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>61,85%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24697</t>
+          <t>24428</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49837</t>
+          <t>47890</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33179</t>
+          <t>32489</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59847</t>
+          <t>58760</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>62710</t>
+          <t>63034</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>98449</t>
+          <t>100111</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41872</t>
+          <t>43675</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67798</t>
+          <t>68078</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10982</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26918</t>
+          <t>25980</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57817</t>
+          <t>57501</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86191</t>
+          <t>85992</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73142</t>
+          <t>74294</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>98648</t>
+          <t>99778</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36449</t>
+          <t>35696</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51895</t>
+          <t>51836</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>115495</t>
+          <t>117541</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>146659</t>
+          <t>147132</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,63%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23784</t>
+          <t>24354</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13139</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30859</t>
+          <t>31332</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17219</t>
+          <t>16538</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33125</t>
+          <t>33285</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12277</t>
+          <t>12431</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>23098</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>42137</t>
+          <t>42027</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,82%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>11623</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26369</t>
+          <t>26718</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13343</t>
+          <t>13928</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18136</t>
+          <t>19486</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>37285</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>53,07%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>15030</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18294</t>
+          <t>18655</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10950</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20894</t>
+          <t>21407</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>13645</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24644</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,41%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12883</t>
+          <t>13478</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>801</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>371901</t>
+          <t>367083</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>443939</t>
+          <t>439573</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>229081</t>
+          <t>229976</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>286122</t>
+          <t>286682</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>621589</t>
+          <t>618292</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>709990</t>
+          <t>712119</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>692007</t>
+          <t>694759</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>769000</t>
+          <t>774568</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>480057</t>
+          <t>477272</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>546715</t>
+          <t>543528</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1191731</t>
+          <t>1191545</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1289279</t>
+          <t>1288048</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,3%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>191076</t>
+          <t>189889</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>245250</t>
+          <t>247602</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>181764</t>
+          <t>182084</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>235736</t>
+          <t>234812</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>383356</t>
+          <t>387055</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>462865</t>
+          <t>464289</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2016</t>
+          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2016 (tasa de respuesta: 98,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18195</t>
+          <t>18500</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36945</t>
+          <t>39284</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14653</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30842</t>
+          <t>30806</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37222</t>
+          <t>36194</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62003</t>
+          <t>63516</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8583,12 +8583,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -8611,12 +8611,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79078</t>
+          <t>77800</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102107</t>
+          <t>102448</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57117</t>
+          <t>55515</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75227</t>
+          <t>75556</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140387</t>
+          <t>141385</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>170954</t>
+          <t>171346</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,43%</t>
         </is>
       </c>
     </row>
@@ -8724,12 +8724,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17396</t>
+          <t>16538</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36570</t>
+          <t>35617</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25070</t>
+          <t>25168</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31290</t>
+          <t>31389</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54685</t>
+          <t>53559</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45783</t>
+          <t>46965</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73209</t>
+          <t>72565</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41640</t>
+          <t>41596</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66503</t>
+          <t>68051</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94818</t>
+          <t>92858</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133159</t>
+          <t>130302</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>154342</t>
+          <t>155456</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>185430</t>
+          <t>185356</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>118651</t>
+          <t>118156</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>145979</t>
+          <t>146049</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>281657</t>
+          <t>282170</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>322315</t>
+          <t>325823</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,86%</t>
         </is>
       </c>
     </row>
@@ -9180,12 +9180,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22861</t>
+          <t>21799</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46210</t>
+          <t>44883</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17685</t>
+          <t>17534</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36471</t>
+          <t>36292</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44673</t>
+          <t>45622</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72547</t>
+          <t>74643</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -9410,12 +9410,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44089</t>
+          <t>42774</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>72714</t>
+          <t>72389</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23815</t>
+          <t>24107</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45344</t>
+          <t>44341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>74925</t>
+          <t>73513</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>106917</t>
+          <t>108476</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9523,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>159902</t>
+          <t>160599</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>193361</t>
+          <t>192484</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>141970</t>
+          <t>143390</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>169332</t>
+          <t>169583</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>313890</t>
+          <t>314443</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>353293</t>
+          <t>355385</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,76%</t>
         </is>
       </c>
     </row>
@@ -9636,12 +9636,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20383</t>
+          <t>21279</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42324</t>
+          <t>42830</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18387</t>
+          <t>18842</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37238</t>
+          <t>38303</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44668</t>
+          <t>42981</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73251</t>
+          <t>73055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38489</t>
+          <t>37718</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66393</t>
+          <t>64907</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32866</t>
+          <t>33501</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58201</t>
+          <t>59016</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9936,12 +9936,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76979</t>
+          <t>79967</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115300</t>
+          <t>115834</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -9979,12 +9979,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>172856</t>
+          <t>173409</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203837</t>
+          <t>205079</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>134408</t>
+          <t>131629</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>165311</t>
+          <t>163887</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>315943</t>
+          <t>313981</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>361840</t>
+          <t>358828</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>70,97%</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10092,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23791</t>
+          <t>24730</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47241</t>
+          <t>48026</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25667</t>
+          <t>24435</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48510</t>
+          <t>48245</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55832</t>
+          <t>55128</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>87735</t>
+          <t>88547</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -10322,12 +10322,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28596</t>
+          <t>28388</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50544</t>
+          <t>51196</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10357,12 +10357,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19183</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40044</t>
+          <t>39246</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10372,12 +10372,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54337</t>
+          <t>52547</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>83689</t>
+          <t>83088</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -10435,12 +10435,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>79790</t>
+          <t>79714</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>104581</t>
+          <t>105060</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10470,12 +10470,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61073</t>
+          <t>59987</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>82405</t>
+          <t>83279</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10505,12 +10505,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>149465</t>
+          <t>146905</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>180020</t>
+          <t>181196</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,71%</t>
         </is>
       </c>
     </row>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8529</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23003</t>
+          <t>22671</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21585</t>
+          <t>22194</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17911</t>
+          <t>18352</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>39764</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -10778,12 +10778,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>10429</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24396</t>
+          <t>24195</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10793,12 +10793,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16269</t>
+          <t>15706</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>18358</t>
+          <t>18758</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>35971</t>
+          <t>36870</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -10891,12 +10891,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30724</t>
+          <t>30854</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44964</t>
+          <t>45394</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9883</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21750</t>
+          <t>21847</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10961,12 +10961,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43884</t>
+          <t>43603</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63277</t>
+          <t>63362</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,79%</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>9394</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11039,12 +11039,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>9954</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11054,12 +11054,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11089,12 +11089,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -11234,12 +11234,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -11304,12 +11304,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9849</t>
+          <t>9277</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20030</t>
+          <t>19561</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11319,12 +11319,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>63,02%</t>
         </is>
       </c>
     </row>
@@ -11347,12 +11347,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17834</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11417,12 +11417,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>11480</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>21764</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11432,12 +11432,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>70,11%</t>
         </is>
       </c>
     </row>
@@ -11460,97 +11460,97 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>1693</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11690,12 +11690,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>230964</t>
+          <t>229114</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>289075</t>
+          <t>286366</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>175320</t>
+          <t>175165</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>225064</t>
+          <t>223493</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>417022</t>
+          <t>418432</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>493559</t>
+          <t>495660</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11775,12 +11775,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -11803,12 +11803,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>740385</t>
+          <t>740944</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>807654</t>
+          <t>807270</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>568218</t>
+          <t>566155</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>623617</t>
+          <t>624421</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1321097</t>
+          <t>1324660</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1408880</t>
+          <t>1411452</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,64%</t>
         </is>
       </c>
     </row>
@@ -11916,12 +11916,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>116593</t>
+          <t>118020</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>163319</t>
+          <t>162662</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>103886</t>
+          <t>101205</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>142982</t>
+          <t>144510</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11966,12 +11966,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>233676</t>
+          <t>232895</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>295304</t>
+          <t>295610</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P24B-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8007</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23979</t>
+          <t>23494</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13229</t>
+          <t>13270</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30627</t>
+          <t>29469</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24547</t>
+          <t>25366</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47313</t>
+          <t>48860</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>125957</t>
+          <t>125807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>152860</t>
+          <t>153710</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84572</t>
+          <t>83209</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>108028</t>
+          <t>108812</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>219848</t>
+          <t>218165</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256073</t>
+          <t>255262</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,08%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40241</t>
+          <t>40054</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63333</t>
+          <t>65782</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41341</t>
+          <t>41144</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64061</t>
+          <t>64127</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>86820</t>
+          <t>86627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>120180</t>
+          <t>120006</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>41119</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68608</t>
+          <t>68885</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40090</t>
+          <t>39494</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65697</t>
+          <t>65175</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87706</t>
+          <t>87041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124438</t>
+          <t>123543</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>273096</t>
+          <t>271726</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>307534</t>
+          <t>308068</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>118043</t>
+          <t>119300</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>147828</t>
+          <t>148918</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>401729</t>
+          <t>401100</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>447856</t>
+          <t>448409</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,85%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43039</t>
+          <t>41421</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71862</t>
+          <t>68953</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36533</t>
+          <t>36126</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61673</t>
+          <t>60365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85059</t>
+          <t>87108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122666</t>
+          <t>124119</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40931</t>
+          <t>42549</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70412</t>
+          <t>68530</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34728</t>
+          <t>34670</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59948</t>
+          <t>60768</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>82640</t>
+          <t>82722</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>121444</t>
+          <t>121832</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>223258</t>
+          <t>221071</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>258871</t>
+          <t>256446</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>150578</t>
+          <t>149769</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>181928</t>
+          <t>181684</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>378530</t>
+          <t>383956</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>430951</t>
+          <t>431159</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,15%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32554</t>
+          <t>33615</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58555</t>
+          <t>60286</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33314</t>
+          <t>33894</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59455</t>
+          <t>58492</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73007</t>
+          <t>73560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>108159</t>
+          <t>110567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21710</t>
+          <t>21198</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43166</t>
+          <t>44471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21089</t>
+          <t>20982</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41583</t>
+          <t>41256</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46550</t>
+          <t>47510</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75258</t>
+          <t>78168</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>160041</t>
+          <t>160899</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188220</t>
+          <t>189816</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80736</t>
+          <t>79695</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104152</t>
+          <t>103228</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>250865</t>
+          <t>249635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>284576</t>
+          <t>284727</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,2%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38662</t>
+          <t>38783</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14842</t>
+          <t>14822</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31188</t>
+          <t>32638</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37670</t>
+          <t>36693</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64592</t>
+          <t>63834</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21064</t>
+          <t>21940</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40193</t>
+          <t>40654</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>15307</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29213</t>
+          <t>28864</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50675</t>
+          <t>51375</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>79449</t>
+          <t>78652</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>99725</t>
+          <t>98831</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23865</t>
+          <t>23210</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37069</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>107150</t>
+          <t>107276</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>130460</t>
+          <t>132271</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>75,33%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15761</t>
+          <t>15260</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10233</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24899</t>
+          <t>24848</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24850</t>
+          <t>24734</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>842</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>13516</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27626</t>
+          <t>27727</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,4%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24075</t>
+          <t>23621</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38213</t>
+          <t>37633</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26899</t>
+          <t>27095</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41260</t>
+          <t>41051</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,7%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9089</t>
+          <t>8834</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>3516</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>19925</t>
+          <t>20209</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>74,06%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12959</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16325</t>
+          <t>15941</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>58,42%</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>189440</t>
+          <t>188031</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>242929</t>
+          <t>242758</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>138394</t>
+          <t>138517</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>184899</t>
+          <t>184218</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>340076</t>
+          <t>344624</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>412919</t>
+          <t>416003</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>939685</t>
+          <t>940290</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1008922</t>
+          <t>1011181</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>499663</t>
+          <t>498398</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>555900</t>
+          <t>553817</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1455238</t>
+          <t>1457953</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1549496</t>
+          <t>1542820</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,67%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>164819</t>
+          <t>165477</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>218636</t>
+          <t>220542</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>155027</t>
+          <t>152141</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>200549</t>
+          <t>200373</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>335610</t>
+          <t>334350</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>405865</t>
+          <t>404758</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33597</t>
+          <t>34794</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57836</t>
+          <t>58274</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24973</t>
+          <t>26217</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47343</t>
+          <t>46817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66746</t>
+          <t>65635</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97246</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69514</t>
+          <t>68565</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95343</t>
+          <t>95038</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56915</t>
+          <t>57056</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82106</t>
+          <t>81013</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133859</t>
+          <t>133221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>169479</t>
+          <t>167719</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,53%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27923</t>
+          <t>28223</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48703</t>
+          <t>50587</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34422</t>
+          <t>32709</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56165</t>
+          <t>55353</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67132</t>
+          <t>67093</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>97718</t>
+          <t>99630</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84389</t>
+          <t>84820</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>118870</t>
+          <t>120517</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61155</t>
+          <t>62219</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89498</t>
+          <t>92733</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>153349</t>
+          <t>155376</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>199306</t>
+          <t>200566</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>169577</t>
+          <t>169846</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>206227</t>
+          <t>208136</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>106081</t>
+          <t>103869</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>137062</t>
+          <t>137068</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>286570</t>
+          <t>283785</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>336012</t>
+          <t>334697</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,0%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47498</t>
+          <t>46650</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76737</t>
+          <t>74854</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39980</t>
+          <t>39733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65323</t>
+          <t>66892</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92702</t>
+          <t>93287</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132102</t>
+          <t>130886</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67546</t>
+          <t>66164</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99657</t>
+          <t>97723</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45928</t>
+          <t>46138</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74792</t>
+          <t>73473</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>122301</t>
+          <t>122156</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>165222</t>
+          <t>162636</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>166310</t>
+          <t>166327</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>201508</t>
+          <t>203016</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115138</t>
+          <t>115773</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147593</t>
+          <t>148224</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>290711</t>
+          <t>291866</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>340612</t>
+          <t>339861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,35%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44373</t>
+          <t>45727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74884</t>
+          <t>75102</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43985</t>
+          <t>43776</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72048</t>
+          <t>72187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96235</t>
+          <t>95637</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>134968</t>
+          <t>135872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65270</t>
+          <t>65802</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97496</t>
+          <t>97049</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46170</t>
+          <t>47237</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75509</t>
+          <t>75424</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120756</t>
+          <t>117547</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163981</t>
+          <t>162268</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145110</t>
+          <t>144683</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>180682</t>
+          <t>179592</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118160</t>
+          <t>119866</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>151781</t>
+          <t>151879</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>273745</t>
+          <t>277462</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>321761</t>
+          <t>323770</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>62,23%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24428</t>
+          <t>24286</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47890</t>
+          <t>49543</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32489</t>
+          <t>32849</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58760</t>
+          <t>59021</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63034</t>
+          <t>64082</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>100111</t>
+          <t>99236</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43675</t>
+          <t>40573</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68078</t>
+          <t>65846</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>11148</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25980</t>
+          <t>26415</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57501</t>
+          <t>57649</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>85992</t>
+          <t>87353</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74294</t>
+          <t>73679</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>99778</t>
+          <t>100267</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35696</t>
+          <t>35399</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51836</t>
+          <t>51874</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>117541</t>
+          <t>115921</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>147132</t>
+          <t>146787</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,47%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24354</t>
+          <t>25113</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11297</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13280</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31332</t>
+          <t>31263</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16538</t>
+          <t>17678</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33285</t>
+          <t>33436</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12431</t>
+          <t>12337</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>23098</t>
+          <t>24132</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>42027</t>
+          <t>42778</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>60,89%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26718</t>
+          <t>26341</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>13932</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19486</t>
+          <t>19118</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37285</t>
+          <t>36606</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15030</t>
+          <t>14463</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8611</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18655</t>
+          <t>19019</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>11104</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13645</t>
+          <t>12938</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24659</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>13611</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,79%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>792</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>367083</t>
+          <t>369359</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>439573</t>
+          <t>445012</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>229976</t>
+          <t>229875</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>286682</t>
+          <t>286355</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>618292</t>
+          <t>624268</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>712119</t>
+          <t>709832</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>694759</t>
+          <t>692557</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>774568</t>
+          <t>769989</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>477272</t>
+          <t>479688</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>543528</t>
+          <t>545286</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1191545</t>
+          <t>1191531</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1288048</t>
+          <t>1289185</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,34%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>189889</t>
+          <t>188328</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>247602</t>
+          <t>245552</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>182084</t>
+          <t>180258</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>234812</t>
+          <t>232260</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>387055</t>
+          <t>387386</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>464289</t>
+          <t>461151</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39284</t>
+          <t>36879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14653</t>
+          <t>14413</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30806</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36194</t>
+          <t>36696</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63516</t>
+          <t>61991</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8583,12 +8583,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -8611,12 +8611,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77800</t>
+          <t>77797</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102448</t>
+          <t>101072</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55515</t>
+          <t>56727</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75556</t>
+          <t>74709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141385</t>
+          <t>140866</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171346</t>
+          <t>171883</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,64%</t>
         </is>
       </c>
     </row>
@@ -8724,12 +8724,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16538</t>
+          <t>17587</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35617</t>
+          <t>36430</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>10287</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25168</t>
+          <t>25297</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31389</t>
+          <t>30998</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53559</t>
+          <t>54026</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46965</t>
+          <t>47188</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72565</t>
+          <t>72499</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41596</t>
+          <t>42392</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68051</t>
+          <t>67016</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>92858</t>
+          <t>95706</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>130302</t>
+          <t>132977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>155456</t>
+          <t>152748</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>185356</t>
+          <t>184221</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>118156</t>
+          <t>118415</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>146049</t>
+          <t>145202</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>282170</t>
+          <t>281266</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>325823</t>
+          <t>322063</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,06%</t>
         </is>
       </c>
     </row>
@@ -9180,12 +9180,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21799</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44883</t>
+          <t>43876</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17534</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36292</t>
+          <t>35277</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45622</t>
+          <t>45487</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74643</t>
+          <t>74912</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -9410,12 +9410,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42774</t>
+          <t>43632</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>72389</t>
+          <t>71989</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24107</t>
+          <t>23606</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44341</t>
+          <t>44866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73513</t>
+          <t>73225</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>108476</t>
+          <t>108565</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9523,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160599</t>
+          <t>160726</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>192484</t>
+          <t>192421</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>143390</t>
+          <t>144492</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>169583</t>
+          <t>169892</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>314443</t>
+          <t>314730</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>355385</t>
+          <t>356160</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,92%</t>
         </is>
       </c>
     </row>
@@ -9636,12 +9636,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21279</t>
+          <t>20949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42830</t>
+          <t>43450</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18842</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38303</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42981</t>
+          <t>44301</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73055</t>
+          <t>73195</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37718</t>
+          <t>37633</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64907</t>
+          <t>65893</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33501</t>
+          <t>33226</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59016</t>
+          <t>57907</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9936,12 +9936,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79967</t>
+          <t>79090</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115834</t>
+          <t>116841</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -9979,12 +9979,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>173409</t>
+          <t>172862</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205079</t>
+          <t>206548</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>131629</t>
+          <t>134025</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>163887</t>
+          <t>162988</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>313981</t>
+          <t>314278</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>358828</t>
+          <t>359241</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10092,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24730</t>
+          <t>23851</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48026</t>
+          <t>48156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24435</t>
+          <t>25224</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48245</t>
+          <t>48475</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55128</t>
+          <t>55432</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>88547</t>
+          <t>88319</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -10322,12 +10322,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28388</t>
+          <t>27509</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>49245</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10357,12 +10357,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19783</t>
+          <t>20795</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39246</t>
+          <t>40763</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10372,12 +10372,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52547</t>
+          <t>53036</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>83088</t>
+          <t>85044</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -10435,12 +10435,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>79714</t>
+          <t>81360</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>105060</t>
+          <t>105960</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10470,12 +10470,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>59987</t>
+          <t>60699</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>83279</t>
+          <t>82107</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10505,12 +10505,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>146905</t>
+          <t>148310</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>181196</t>
+          <t>181595</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,87%</t>
         </is>
       </c>
     </row>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22671</t>
+          <t>22697</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22194</t>
+          <t>23139</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>18144</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39764</t>
+          <t>39592</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -10778,12 +10778,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10429</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24195</t>
+          <t>24486</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10793,12 +10793,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>18758</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36870</t>
+          <t>35959</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>40,74%</t>
         </is>
       </c>
     </row>
@@ -10891,12 +10891,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30854</t>
+          <t>30044</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45394</t>
+          <t>45276</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10140</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21847</t>
+          <t>21467</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10961,12 +10961,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43603</t>
+          <t>45372</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63362</t>
+          <t>62930</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,3%</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9394</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11039,12 +11039,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9954</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11054,12 +11054,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>15502</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11089,12 +11089,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -11234,12 +11234,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13500</t>
+          <t>13491</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -11304,12 +11304,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9277</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>19561</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11319,12 +11319,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>64,44%</t>
         </is>
       </c>
     </row>
@@ -11347,12 +11347,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9527</t>
+          <t>9536</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17536</t>
+          <t>17957</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11417,12 +11417,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21764</t>
+          <t>21418</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11432,12 +11432,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,0%</t>
         </is>
       </c>
     </row>
@@ -11690,12 +11690,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>229114</t>
+          <t>229356</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>286366</t>
+          <t>287286</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>175165</t>
+          <t>174032</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>223493</t>
+          <t>226002</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>418432</t>
+          <t>420110</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>495660</t>
+          <t>495334</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11775,12 +11775,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -11803,12 +11803,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>740944</t>
+          <t>741170</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>807270</t>
+          <t>806208</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>566155</t>
+          <t>568299</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>624421</t>
+          <t>627045</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1324660</t>
+          <t>1325833</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1411452</t>
+          <t>1410439</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,59%</t>
         </is>
       </c>
     </row>
@@ -11916,12 +11916,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>118020</t>
+          <t>118603</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>162662</t>
+          <t>165825</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>101205</t>
+          <t>103362</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>144510</t>
+          <t>145935</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11966,12 +11966,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>232895</t>
+          <t>231646</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>295610</t>
+          <t>292687</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
